--- a/artfynd/A 21106-2023 artfynd.xlsx
+++ b/artfynd/A 21106-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21106-2023 artfynd.xlsx
+++ b/artfynd/A 21106-2023 artfynd.xlsx
@@ -1409,7 +1409,7 @@
         <v>81883094</v>
       </c>
       <c r="B8" t="n">
-        <v>56366</v>
+        <v>57447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629210.7430146224</v>
+        <v>629211</v>
       </c>
       <c r="R8" t="n">
-        <v>6894484.961886272</v>
+        <v>6894485</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>

--- a/artfynd/A 21106-2023 artfynd.xlsx
+++ b/artfynd/A 21106-2023 artfynd.xlsx
@@ -1409,7 +1409,7 @@
         <v>81883094</v>
       </c>
       <c r="B8" t="n">
-        <v>57447</v>
+        <v>57450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 21106-2023 artfynd.xlsx
+++ b/artfynd/A 21106-2023 artfynd.xlsx
@@ -1409,7 +1409,7 @@
         <v>81883094</v>
       </c>
       <c r="B8" t="n">
-        <v>57450</v>
+        <v>57456</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 21106-2023 artfynd.xlsx
+++ b/artfynd/A 21106-2023 artfynd.xlsx
@@ -1409,7 +1409,7 @@
         <v>81883094</v>
       </c>
       <c r="B8" t="n">
-        <v>57456</v>
+        <v>57459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 21106-2023 artfynd.xlsx
+++ b/artfynd/A 21106-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,7 +1409,7 @@
         <v>81883094</v>
       </c>
       <c r="B8" t="n">
-        <v>57459</v>
+        <v>57460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115209239</v>
+        <v>115357393</v>
       </c>
       <c r="B15" t="n">
-        <v>57943</v>
+        <v>56323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,37 +2271,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>100045</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2341,22 +2341,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,22 +2371,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Olsson</t>
+          <t>Leif Strandberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Olsson</t>
+          <t>Leif Strandberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115357393</v>
+        <v>117258235</v>
       </c>
       <c r="B16" t="n">
-        <v>56323</v>
+        <v>57715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2395,39 +2395,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100045</v>
+        <v>103001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2465,22 +2461,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2495,22 +2491,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Leif Strandberg</t>
+          <t>Ulf Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Leif Strandberg</t>
+          <t>Ulf Lindberg, Åsa Granlöf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117258235</v>
+        <v>117434636</v>
       </c>
       <c r="B17" t="n">
-        <v>57715</v>
+        <v>57828</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2519,35 +2515,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2585,22 +2585,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,263 +2615,15 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulf Lindberg</t>
+          <t>Bengt-Olof  Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulf Lindberg, Åsa Granlöf</t>
+          <t>Bengt-Olof  Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>117434636</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57828</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>102990</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Prunella modularis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Palmtorpet, Gubbrå, Njurunda, Mpd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>629211</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6894485</v>
-      </c>
-      <c r="S18" t="n">
-        <v>50</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Njurunda</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Bengt-Olof  Nilsson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Bengt-Olof  Nilsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>117434647</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57203</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Haliaeetus albicilla</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Palmtorpet, Gubbrå, Njurunda, Mpd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>629211</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6894485</v>
-      </c>
-      <c r="S19" t="n">
-        <v>50</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Njurunda</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Bengt-Olof  Nilsson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Bengt-Olof  Nilsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
